--- a/sample_data/ACL-Intake-Form.xlsx
+++ b/sample_data/ACL-Intake-Form.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{6E9A4202-D9CE-C840-B731-0A4F6C06D9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42CB49F6-A77A-AB41-AB11-52B01D090622}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{6E9A4202-D9CE-C840-B731-0A4F6C06D9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C812D5AD-F0F3-314A-BAB7-CB9FBD1281FB}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{8CD9028D-EAA5-1540-B491-1BAEAEAE6A66}"/>
   </bookViews>

--- a/sample_data/ACL-Intake-Form.xlsx
+++ b/sample_data/ACL-Intake-Form.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{6E9A4202-D9CE-C840-B731-0A4F6C06D9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C812D5AD-F0F3-314A-BAB7-CB9FBD1281FB}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{6E9A4202-D9CE-C840-B731-0A4F6C06D9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{139593B3-B89D-DB4B-8848-6A94548D08B4}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{8CD9028D-EAA5-1540-B491-1BAEAEAE6A66}"/>
   </bookViews>
@@ -531,7 +531,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="1">
-        <v>45840</v>
+        <v>45945</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
@@ -540,7 +540,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="1">
-        <v>45848</v>
+        <v>45973</v>
       </c>
       <c r="L2" t="s">
         <v>14</v>

--- a/sample_data/ACL-Intake-Form.xlsx
+++ b/sample_data/ACL-Intake-Form.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csip-my.sharepoint.com/personal/akates_csipacific_ca/Documents/CSI-Pacific-RTP/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{6E9A4202-D9CE-C840-B731-0A4F6C06D9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{139593B3-B89D-DB4B-8848-6A94548D08B4}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{6E9A4202-D9CE-C840-B731-0A4F6C06D9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E6C60B8-17E7-A046-B433-2E7B5A78302E}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{8CD9028D-EAA5-1540-B491-1BAEAEAE6A66}"/>
   </bookViews>
